--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260625.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,278,000</t>
+          <t>2,664,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,664,000</t>
+          <t>14,278,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
